--- a/balance_tables/食客.xlsx
+++ b/balance_tables/食客.xlsx
@@ -1,179 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{516D3A1C-17BA-4776-8781-7A354578F9E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="配置" sheetId="1" r:id="rId1"/>
-    <sheet name="食客" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食客" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
-  <si>
-    <t>参数ID</t>
-  </si>
-  <si>
-    <t>数值</t>
-  </si>
-  <si>
-    <t>说明</t>
-  </si>
-  <si>
-    <t>schema_id</t>
-  </si>
-  <si>
-    <t>xiaochuxi.customers</t>
-  </si>
-  <si>
-    <t>食客数值表结构标识，请勿修改</t>
-  </si>
-  <si>
-    <t>schema_version</t>
-  </si>
-  <si>
-    <t>结构版本；不兼容修改时递增</t>
-  </si>
-  <si>
-    <t>启用</t>
-  </si>
-  <si>
-    <t>食客ID</t>
-  </si>
-  <si>
-    <t>显示名称</t>
-  </si>
-  <si>
-    <t>身份层级</t>
-  </si>
-  <si>
-    <t>行为类型</t>
-  </si>
-  <si>
-    <t>胃口倍率</t>
-  </si>
-  <si>
-    <t>移动速度(px/s)</t>
-  </si>
-  <si>
-    <t>占据区域数</t>
-  </si>
-  <si>
-    <t>攻击强度比例</t>
-  </si>
-  <si>
-    <t>攻击间隔(s)</t>
-  </si>
-  <si>
-    <t>颜色HEX</t>
-  </si>
-  <si>
-    <t>basic_guest</t>
-  </si>
-  <si>
-    <t>普通</t>
-  </si>
-  <si>
-    <t>无</t>
-  </si>
-  <si>
-    <t>#63784F</t>
-  </si>
-  <si>
-    <t>fast_guest</t>
-  </si>
-  <si>
-    <t>#8C5940</t>
-  </si>
-  <si>
-    <t>ranged_guest</t>
-  </si>
-  <si>
-    <t>远程</t>
-  </si>
-  <si>
-    <t>#594F7A</t>
-  </si>
-  <si>
-    <t>elite_guest</t>
-  </si>
-  <si>
-    <t>六席贵客</t>
-  </si>
-  <si>
-    <t>精英</t>
-  </si>
-  <si>
-    <t>#82403D</t>
-  </si>
-  <si>
-    <t>饿饿小鼠</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>急急狐狸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>肥肥青蛙</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="0.0"/>
+    <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
-      <b/>
+      <name val="Carlito"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Carlito"/>
     </font>
     <font>
+      <name val="Carlito"/>
       <sz val="11"/>
-      <name val="Carlito"/>
     </font>
     <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <family val="3"/>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
     </font>
     <font>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+      <family val="2"/>
       <sz val="11"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -266,96 +142,161 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="21">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CustomersTable" displayName="CustomersTable" ref="A1:K5" totalsRowShown="0">
-  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CustomersTable" displayName="CustomersTable" ref="A1:K5" headerRowCount="1" totalsRowShown="0">
+  <autoFilter ref="A1:K5"/>
   <tableColumns count="11">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="启用"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="食客ID"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="显示名称"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="身份层级"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="行为类型"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="胃口倍率"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="移动速度(px/s)"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="占据区域数"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="攻击强度比例"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻击间隔(s)"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="颜色HEX"/>
+    <tableColumn id="1" name="启用"/>
+    <tableColumn id="2" name="食客ID"/>
+    <tableColumn id="3" name="显示名称"/>
+    <tableColumn id="4" name="身份层级"/>
+    <tableColumn id="5" name="行为类型"/>
+    <tableColumn id="6" name="胃口倍率"/>
+    <tableColumn id="7" name="移动速度(px/s)"/>
+    <tableColumn id="8" name="占据区域数"/>
+    <tableColumn id="9" name="攻击强度比例"/>
+    <tableColumn id="10" name="攻击间隔(s)"/>
+    <tableColumn id="11" name="颜色HEX"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -555,254 +496,338 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="22" style="1" customWidth="1"/>
-    <col min="2" max="2" width="26" style="1" customWidth="1"/>
-    <col min="3" max="3" width="38" style="1" customWidth="1"/>
+    <col width="22" customWidth="1" style="1" min="1" max="1"/>
+    <col width="26" customWidth="1" style="1" min="2" max="2"/>
+    <col width="38" customWidth="1" style="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="24" customHeight="1">
-      <c r="A1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="2" t="s">
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>参数ID</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="inlineStr">
+        <is>
+          <t>数值</t>
+        </is>
+      </c>
+      <c r="C1" s="2" t="inlineStr">
+        <is>
+          <t>说明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>schema_id</t>
+        </is>
+      </c>
+      <c r="B2" s="4" t="inlineStr">
+        <is>
+          <t>xiaochuxi.customers</t>
+        </is>
+      </c>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>食客数值表结构标识，请勿修改</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="inlineStr">
+        <is>
+          <t>schema_version</t>
+        </is>
+      </c>
+      <c r="B3" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" ht="24" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="6">
-        <v>1</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>7</v>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>结构版本；不兼容修改时递增</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K5"/>
-  <sheetFormatPr defaultRowHeight="13.8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="1" width="9" style="1" customWidth="1"/>
-    <col min="2" max="2" width="20" style="1" customWidth="1"/>
-    <col min="3" max="3" width="15" style="1" customWidth="1"/>
-    <col min="4" max="6" width="12" style="1" customWidth="1"/>
-    <col min="7" max="7" width="19" style="1" customWidth="1"/>
-    <col min="8" max="8" width="14" style="1" customWidth="1"/>
-    <col min="9" max="9" width="17" style="1" customWidth="1"/>
-    <col min="10" max="10" width="15" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14" style="1" customWidth="1"/>
+    <col width="9" customWidth="1" style="1" min="1" max="1"/>
+    <col width="20" customWidth="1" style="1" min="2" max="2"/>
+    <col width="15" customWidth="1" style="1" min="3" max="3"/>
+    <col width="12" customWidth="1" style="1" min="4" max="6"/>
+    <col width="19" customWidth="1" style="1" min="7" max="7"/>
+    <col width="14" customWidth="1" style="1" min="8" max="8"/>
+    <col width="17" customWidth="1" style="1" min="9" max="9"/>
+    <col width="15" customWidth="1" style="1" min="10" max="10"/>
+    <col width="14" customWidth="1" style="1" min="11" max="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="34.049999999999997" customHeight="1">
-      <c r="A1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="J1" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="K1" s="7" t="s">
-        <v>18</v>
+    <row r="1" ht="34.05" customHeight="1">
+      <c r="A1" s="7" t="inlineStr">
+        <is>
+          <t>启用</t>
+        </is>
+      </c>
+      <c r="B1" s="7" t="inlineStr">
+        <is>
+          <t>食客ID</t>
+        </is>
+      </c>
+      <c r="C1" s="7" t="inlineStr">
+        <is>
+          <t>显示名称</t>
+        </is>
+      </c>
+      <c r="D1" s="7" t="inlineStr">
+        <is>
+          <t>身份层级</t>
+        </is>
+      </c>
+      <c r="E1" s="7" t="inlineStr">
+        <is>
+          <t>行为类型</t>
+        </is>
+      </c>
+      <c r="F1" s="7" t="inlineStr">
+        <is>
+          <t>胃口倍率</t>
+        </is>
+      </c>
+      <c r="G1" s="7" t="inlineStr">
+        <is>
+          <t>移动速度(px/s)</t>
+        </is>
+      </c>
+      <c r="H1" s="7" t="inlineStr">
+        <is>
+          <t>占据区域数</t>
+        </is>
+      </c>
+      <c r="I1" s="7" t="inlineStr">
+        <is>
+          <t>攻击强度比例</t>
+        </is>
+      </c>
+      <c r="J1" s="7" t="inlineStr">
+        <is>
+          <t>攻击间隔(s)</t>
+        </is>
+      </c>
+      <c r="K1" s="7" t="inlineStr">
+        <is>
+          <t>颜色HEX</t>
+        </is>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="24" customHeight="1">
+    <row r="2" ht="24" customHeight="1">
       <c r="A2" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="s">
-        <v>19</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="12">
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>basic_guest</t>
+        </is>
+      </c>
+      <c r="C2" s="18" t="inlineStr">
+        <is>
+          <t>饿饿小鼠</t>
+        </is>
+      </c>
+      <c r="D2" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E2" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="G2" s="13">
+      <c r="G2" s="13" t="n">
         <v>42</v>
       </c>
-      <c r="H2" s="13">
+      <c r="H2" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I2" s="12"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="9" t="s">
-        <v>22</v>
+      <c r="I2" s="12" t="n"/>
+      <c r="J2" s="19" t="n"/>
+      <c r="K2" s="9" t="inlineStr">
+        <is>
+          <t>#63784F</t>
+        </is>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="24" customHeight="1">
+    <row r="3" ht="24" customHeight="1">
       <c r="A3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>21</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="B3" s="8" t="inlineStr">
+        <is>
+          <t>fast_guest</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>急急狐狸</t>
+        </is>
+      </c>
+      <c r="D3" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E3" s="8" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F3" s="12" t="n">
         <v>0.75</v>
       </c>
-      <c r="G3" s="13">
+      <c r="G3" s="13" t="n">
         <v>96</v>
       </c>
-      <c r="H3" s="13">
+      <c r="H3" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I3" s="12"/>
-      <c r="J3" s="14"/>
-      <c r="K3" s="9" t="s">
-        <v>24</v>
+      <c r="I3" s="12" t="n"/>
+      <c r="J3" s="19" t="n"/>
+      <c r="K3" s="9" t="inlineStr">
+        <is>
+          <t>#8C5940</t>
+        </is>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="24" customHeight="1">
+    <row r="4" ht="24" customHeight="1">
       <c r="A4" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="18" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>20</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="F4" s="12">
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>ranged_guest</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>肥肥青蛙</t>
+        </is>
+      </c>
+      <c r="D4" s="8" t="inlineStr">
+        <is>
+          <t>普通</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>远程</t>
+        </is>
+      </c>
+      <c r="F4" s="12" t="n">
         <v>1.5</v>
       </c>
-      <c r="G4" s="13">
+      <c r="G4" s="13" t="n">
         <v>28</v>
       </c>
-      <c r="H4" s="13">
+      <c r="H4" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="12" t="n">
         <v>0.08</v>
       </c>
-      <c r="J4" s="14">
+      <c r="J4" s="19" t="n">
         <v>3.4</v>
       </c>
-      <c r="K4" s="9" t="s">
-        <v>27</v>
+      <c r="K4" s="9" t="inlineStr">
+        <is>
+          <t>#594F7A</t>
+        </is>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="24" customHeight="1">
+    <row r="5" ht="24" customHeight="1">
       <c r="A5" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F5" s="15">
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>elite_guest</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>六席贵客</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>精英</t>
+        </is>
+      </c>
+      <c r="E5" s="10" t="inlineStr">
+        <is>
+          <t>无</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="n">
         <v>1.5</v>
       </c>
-      <c r="G5" s="16">
-        <v>18</v>
-      </c>
-      <c r="H5" s="16">
+      <c r="G5" s="16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="16" t="n">
         <v>6</v>
       </c>
-      <c r="I5" s="15"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="11" t="s">
-        <v>31</v>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="20" t="n"/>
+      <c r="K5" s="11" t="inlineStr">
+        <is>
+          <t>#82403D</t>
+        </is>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation type="list" sqref="A2:A200" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"普通,精英"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="E2:E200" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
       <formula1>"无,远程"</formula1>
     </dataValidation>
-    <dataValidation type="whole" sqref="H2:H200" xr:uid="{00000000-0002-0000-0100-000003000000}">
+    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
       <formula1>1</formula1>
       <formula2>6</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" paperSize="9"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>
--- a/balance_tables/食客.xlsx
+++ b/balance_tables/食客.xlsx
@@ -1,55 +1,176 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gameproduct\小厨西\balance_tables\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6996145-8DD3-42C0-9A09-A852410615B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="配置" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="食客" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="配置" sheetId="1" r:id="rId1"/>
+    <sheet name="食客" sheetId="2" r:id="rId2"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+  <si>
+    <t>参数ID</t>
+  </si>
+  <si>
+    <t>数值</t>
+  </si>
+  <si>
+    <t>说明</t>
+  </si>
+  <si>
+    <t>schema_id</t>
+  </si>
+  <si>
+    <t>xiaochuxi.customers</t>
+  </si>
+  <si>
+    <t>食客数值表结构标识，请勿修改</t>
+  </si>
+  <si>
+    <t>schema_version</t>
+  </si>
+  <si>
+    <t>结构版本；不兼容修改时递增</t>
+  </si>
+  <si>
+    <t>启用</t>
+  </si>
+  <si>
+    <t>食客ID</t>
+  </si>
+  <si>
+    <t>显示名称</t>
+  </si>
+  <si>
+    <t>身份层级</t>
+  </si>
+  <si>
+    <t>行为类型</t>
+  </si>
+  <si>
+    <t>胃口倍率</t>
+  </si>
+  <si>
+    <t>移动速度(px/s)</t>
+  </si>
+  <si>
+    <t>占据区域数</t>
+  </si>
+  <si>
+    <t>攻击强度比例</t>
+  </si>
+  <si>
+    <t>攻击间隔(s)</t>
+  </si>
+  <si>
+    <t>颜色HEX</t>
+  </si>
+  <si>
+    <t>basic_guest</t>
+  </si>
+  <si>
+    <t>饿饿小鼠</t>
+  </si>
+  <si>
+    <t>普通</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>#63784F</t>
+  </si>
+  <si>
+    <t>fast_guest</t>
+  </si>
+  <si>
+    <t>急急狐狸</t>
+  </si>
+  <si>
+    <t>#8C5940</t>
+  </si>
+  <si>
+    <t>ranged_guest</t>
+  </si>
+  <si>
+    <t>肥肥青蛙</t>
+  </si>
+  <si>
+    <t>远程</t>
+  </si>
+  <si>
+    <t>#594F7A</t>
+  </si>
+  <si>
+    <t>elite_guest</t>
+  </si>
+  <si>
+    <t>六席贵客</t>
+  </si>
+  <si>
+    <t>精英</t>
+  </si>
+  <si>
+    <t>#82403D</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="176" formatCode="0.0"/>
   </numFmts>
   <fonts count="5">
     <font>
+      <sz val="11"/>
       <name val="Carlito"/>
-      <sz val="11"/>
     </font>
     <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="Carlito"/>
-      <b val="1"/>
-      <color rgb="FFFFFFFF"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="Carlito"/>
-      <sz val="11"/>
     </font>
     <font>
+      <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-      <family val="3"/>
-      <sz val="9"/>
     </font>
     <font>
+      <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-      <family val="2"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="5">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -142,161 +263,96 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+  <cellXfs count="19">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="2" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="1" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="1">
+    <xf numFmtId="176" fontId="0" fillId="4" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
+    <cellStyle name="Normal" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal" xfId="1"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="CustomersTable" displayName="CustomersTable" ref="A1:K5" headerRowCount="1" totalsRowShown="0">
-  <autoFilter ref="A1:K5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="CustomersTable" displayName="CustomersTable" ref="A1:K5" totalsRowShown="0">
+  <autoFilter ref="A1:K5" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="11">
-    <tableColumn id="1" name="启用"/>
-    <tableColumn id="2" name="食客ID"/>
-    <tableColumn id="3" name="显示名称"/>
-    <tableColumn id="4" name="身份层级"/>
-    <tableColumn id="5" name="行为类型"/>
-    <tableColumn id="6" name="胃口倍率"/>
-    <tableColumn id="7" name="移动速度(px/s)"/>
-    <tableColumn id="8" name="占据区域数"/>
-    <tableColumn id="9" name="攻击强度比例"/>
-    <tableColumn id="10" name="攻击间隔(s)"/>
-    <tableColumn id="11" name="颜色HEX"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="启用"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="食客ID"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="显示名称"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="身份层级"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="行为类型"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="胃口倍率"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="移动速度(px/s)"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="占据区域数"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="攻击强度比例"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="攻击间隔(s)"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="颜色HEX"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -496,338 +552,254 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col width="22" customWidth="1" style="1" min="1" max="1"/>
-    <col width="26" customWidth="1" style="1" min="2" max="2"/>
-    <col width="38" customWidth="1" style="1" min="3" max="3"/>
+    <col min="1" max="1" width="22" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26" style="1" customWidth="1"/>
+    <col min="3" max="3" width="38" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>参数ID</t>
-        </is>
-      </c>
-      <c r="B1" s="2" t="inlineStr">
-        <is>
-          <t>数值</t>
-        </is>
-      </c>
-      <c r="C1" s="2" t="inlineStr">
-        <is>
-          <t>说明</t>
-        </is>
+    <row r="1" spans="1:3" ht="24" customHeight="1">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>schema_id</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>xiaochuxi.customers</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>食客数值表结构标识，请勿修改</t>
-        </is>
+    <row r="2" spans="1:3" ht="24" customHeight="1">
+      <c r="A2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="5" t="inlineStr">
-        <is>
-          <t>schema_version</t>
-        </is>
-      </c>
-      <c r="B3" s="6" t="n">
+    <row r="3" spans="1:3" ht="24" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>结构版本；不兼容修改时递增</t>
-        </is>
+      <c r="C3" s="5" t="s">
+        <v>7</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:K5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.8"/>
+  <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
-    <col width="9" customWidth="1" style="1" min="1" max="1"/>
-    <col width="20" customWidth="1" style="1" min="2" max="2"/>
-    <col width="15" customWidth="1" style="1" min="3" max="3"/>
-    <col width="12" customWidth="1" style="1" min="4" max="6"/>
-    <col width="19" customWidth="1" style="1" min="7" max="7"/>
-    <col width="14" customWidth="1" style="1" min="8" max="8"/>
-    <col width="17" customWidth="1" style="1" min="9" max="9"/>
-    <col width="15" customWidth="1" style="1" min="10" max="10"/>
-    <col width="14" customWidth="1" style="1" min="11" max="11"/>
+    <col min="1" max="1" width="9" style="1" customWidth="1"/>
+    <col min="2" max="2" width="20" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15" style="1" customWidth="1"/>
+    <col min="4" max="6" width="12" style="1" customWidth="1"/>
+    <col min="7" max="7" width="19" style="1" customWidth="1"/>
+    <col min="8" max="8" width="14" style="1" customWidth="1"/>
+    <col min="9" max="9" width="17" style="1" customWidth="1"/>
+    <col min="10" max="10" width="15" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="34.05" customHeight="1">
-      <c r="A1" s="7" t="inlineStr">
-        <is>
-          <t>启用</t>
-        </is>
-      </c>
-      <c r="B1" s="7" t="inlineStr">
-        <is>
-          <t>食客ID</t>
-        </is>
-      </c>
-      <c r="C1" s="7" t="inlineStr">
-        <is>
-          <t>显示名称</t>
-        </is>
-      </c>
-      <c r="D1" s="7" t="inlineStr">
-        <is>
-          <t>身份层级</t>
-        </is>
-      </c>
-      <c r="E1" s="7" t="inlineStr">
-        <is>
-          <t>行为类型</t>
-        </is>
-      </c>
-      <c r="F1" s="7" t="inlineStr">
-        <is>
-          <t>胃口倍率</t>
-        </is>
-      </c>
-      <c r="G1" s="7" t="inlineStr">
-        <is>
-          <t>移动速度(px/s)</t>
-        </is>
-      </c>
-      <c r="H1" s="7" t="inlineStr">
-        <is>
-          <t>占据区域数</t>
-        </is>
-      </c>
-      <c r="I1" s="7" t="inlineStr">
-        <is>
-          <t>攻击强度比例</t>
-        </is>
-      </c>
-      <c r="J1" s="7" t="inlineStr">
-        <is>
-          <t>攻击间隔(s)</t>
-        </is>
-      </c>
-      <c r="K1" s="7" t="inlineStr">
-        <is>
-          <t>颜色HEX</t>
-        </is>
+    <row r="1" spans="1:11" ht="34.049999999999997" customHeight="1">
+      <c r="A1" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E1" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="G1" s="7" t="s">
+        <v>14</v>
+      </c>
+      <c r="H1" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="I1" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="J1" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K1" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="2" ht="24" customHeight="1">
+    <row r="2" spans="1:11" ht="24" customHeight="1">
       <c r="A2" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B2" s="8" t="inlineStr">
-        <is>
-          <t>basic_guest</t>
-        </is>
-      </c>
-      <c r="C2" s="18" t="inlineStr">
-        <is>
-          <t>饿饿小鼠</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="E2" s="8" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F2" s="12" t="n">
+      <c r="B2" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F2" s="12">
         <v>1</v>
       </c>
-      <c r="G2" s="13" t="n">
+      <c r="G2" s="13">
         <v>42</v>
       </c>
-      <c r="H2" s="13" t="n">
+      <c r="H2" s="13">
         <v>2</v>
       </c>
-      <c r="I2" s="12" t="n"/>
-      <c r="J2" s="19" t="n"/>
-      <c r="K2" s="9" t="inlineStr">
-        <is>
-          <t>#63784F</t>
-        </is>
+      <c r="I2" s="12"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="9" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="3" ht="24" customHeight="1">
+    <row r="3" spans="1:11" ht="24" customHeight="1">
       <c r="A3" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B3" s="8" t="inlineStr">
-        <is>
-          <t>fast_guest</t>
-        </is>
-      </c>
-      <c r="C3" s="18" t="inlineStr">
-        <is>
-          <t>急急狐狸</t>
-        </is>
-      </c>
-      <c r="D3" s="8" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="E3" s="8" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F3" s="12" t="n">
+      <c r="B3" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="16" t="s">
+        <v>25</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F3" s="12">
         <v>0.75</v>
       </c>
-      <c r="G3" s="13" t="n">
+      <c r="G3" s="13">
         <v>96</v>
       </c>
-      <c r="H3" s="13" t="n">
+      <c r="H3" s="13">
         <v>2</v>
       </c>
-      <c r="I3" s="12" t="n"/>
-      <c r="J3" s="19" t="n"/>
-      <c r="K3" s="9" t="inlineStr">
-        <is>
-          <t>#8C5940</t>
-        </is>
+      <c r="I3" s="12"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="9" t="s">
+        <v>26</v>
       </c>
     </row>
-    <row r="4" ht="24" customHeight="1">
+    <row r="4" spans="1:11" ht="24" customHeight="1">
       <c r="A4" s="9" t="b">
         <v>1</v>
       </c>
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>ranged_guest</t>
-        </is>
-      </c>
-      <c r="C4" s="18" t="inlineStr">
-        <is>
-          <t>肥肥青蛙</t>
-        </is>
-      </c>
-      <c r="D4" s="8" t="inlineStr">
-        <is>
-          <t>普通</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr">
-        <is>
-          <t>远程</t>
-        </is>
-      </c>
-      <c r="F4" s="12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="G4" s="13" t="n">
+      <c r="B4" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="H4" s="13" t="n">
+      <c r="D4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="12">
+        <v>1.25</v>
+      </c>
+      <c r="G4" s="13">
+        <v>28</v>
+      </c>
+      <c r="H4" s="13">
         <v>2</v>
       </c>
-      <c r="I4" s="12" t="n">
+      <c r="I4" s="12">
         <v>0.08</v>
       </c>
-      <c r="J4" s="19" t="n">
+      <c r="J4" s="17">
         <v>3.4</v>
       </c>
-      <c r="K4" s="9" t="inlineStr">
-        <is>
-          <t>#594F7A</t>
-        </is>
+      <c r="K4" s="9" t="s">
+        <v>30</v>
       </c>
     </row>
-    <row r="5" ht="24" customHeight="1">
+    <row r="5" spans="1:11" ht="24" customHeight="1">
       <c r="A5" s="11" t="b">
         <v>1</v>
       </c>
-      <c r="B5" s="10" t="inlineStr">
-        <is>
-          <t>elite_guest</t>
-        </is>
-      </c>
-      <c r="C5" s="10" t="inlineStr">
-        <is>
-          <t>六席贵客</t>
-        </is>
-      </c>
-      <c r="D5" s="10" t="inlineStr">
-        <is>
-          <t>精英</t>
-        </is>
-      </c>
-      <c r="E5" s="10" t="inlineStr">
-        <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="F5" s="15" t="n">
+      <c r="B5" s="10" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="14">
         <v>1.5</v>
       </c>
-      <c r="G5" s="16" t="n">
+      <c r="G5" s="15">
         <v>0</v>
       </c>
-      <c r="H5" s="16" t="n">
+      <c r="H5" s="15">
         <v>6</v>
       </c>
-      <c r="I5" s="15" t="n"/>
-      <c r="J5" s="20" t="n"/>
-      <c r="K5" s="11" t="inlineStr">
-        <is>
-          <t>#82403D</t>
-        </is>
+      <c r="I5" s="14"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="3" type="noConversion"/>
   <dataValidations count="4">
-    <dataValidation sqref="A2:A200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="A2:A200" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"true,false"</formula1>
     </dataValidation>
-    <dataValidation sqref="D2:D200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="D2:D200" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"普通,精英"</formula1>
     </dataValidation>
-    <dataValidation sqref="E2:E200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="E2:E200" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"无,远程"</formula1>
     </dataValidation>
-    <dataValidation sqref="H2:H200" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="whole">
+    <dataValidation type="whole" sqref="H2:H200" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>1</formula1>
       <formula2>6</formula2>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>